--- a/exports/trend_1d/BPCL_full_report.xlsx
+++ b/exports/trend_1d/BPCL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:U85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.82</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H2" t="n">
-        <v>110.4</v>
+        <v>102.95</v>
       </c>
       <c r="I2" t="n">
         <v>104.907080562072</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K2" t="n">
-        <v>19.67</v>
+        <v>11.6</v>
       </c>
       <c r="L2" t="n">
         <v>3.36</v>
@@ -555,7 +578,7 @@
         <v>2.03</v>
       </c>
       <c r="N2" t="n">
-        <v>3.86</v>
+        <v>6.75</v>
       </c>
       <c r="O2" t="n">
         <v>1.93</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>14.82</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42151</v>
+        <v>42152</v>
       </c>
       <c r="H3" t="n">
-        <v>112.85</v>
+        <v>116.1</v>
       </c>
       <c r="I3" t="n">
         <v>114.0772350103659</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" t="n">
-        <v>-9.619999999999999</v>
+        <v>-12.77</v>
       </c>
       <c r="L3" t="n">
-        <v>10.98</v>
+        <v>13.65</v>
       </c>
       <c r="M3" t="n">
         <v>2.24</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.43</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42193</v>
+        <v>42194</v>
       </c>
       <c r="H4" t="n">
-        <v>131.25</v>
+        <v>123.6</v>
       </c>
       <c r="I4" t="n">
         <v>124.412594093311</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K4" t="n">
-        <v>13.05</v>
+        <v>6.46</v>
       </c>
       <c r="L4" t="n">
         <v>2.93</v>
@@ -669,7 +716,7 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.83</v>
+        <v>5.83</v>
       </c>
       <c r="O4" t="n">
         <v>2.88</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>12.79</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42202</v>
+        <v>42205</v>
       </c>
       <c r="H5" t="n">
-        <v>134.8</v>
+        <v>138.55</v>
       </c>
       <c r="I5" t="n">
         <v>136.8663189059762</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.06</v>
+        <v>-12.1</v>
       </c>
       <c r="L5" t="n">
-        <v>10.44</v>
+        <v>12.62</v>
       </c>
       <c r="M5" t="n">
-        <v>0.65</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
         <v>3.38</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>9.17</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42227</v>
+        <v>42228</v>
       </c>
       <c r="H6" t="n">
-        <v>132.6</v>
+        <v>124.15</v>
       </c>
       <c r="I6" t="n">
         <v>129.2459989203667</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.29</v>
+        <v>-10.39</v>
       </c>
       <c r="L6" t="n">
-        <v>6.57</v>
+        <v>11.04</v>
       </c>
       <c r="M6" t="n">
         <v>0.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.46</v>
+        <v>6.37</v>
       </c>
       <c r="O6" t="n">
         <v>2.78</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>15.15</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42293</v>
+        <v>42296</v>
       </c>
       <c r="H7" t="n">
-        <v>130.45</v>
+        <v>131.6</v>
       </c>
       <c r="I7" t="n">
         <v>131.4698549435441</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.07</v>
+        <v>-6</v>
       </c>
       <c r="L7" t="n">
         <v>7.57</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.5</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42394</v>
+        <v>42396</v>
       </c>
       <c r="H8" t="n">
-        <v>125.3</v>
+        <v>124.2</v>
       </c>
       <c r="I8" t="n">
         <v>124.4274229145614</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.79</v>
+        <v>-5.62</v>
       </c>
       <c r="L8" t="n">
         <v>6.69</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.41</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42445</v>
+        <v>42446</v>
       </c>
       <c r="H9" t="n">
-        <v>116.2</v>
+        <v>123.3</v>
       </c>
       <c r="I9" t="n">
         <v>118.9740843547946</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K9" t="n">
-        <v>6.44</v>
+        <v>0.72</v>
       </c>
       <c r="L9" t="n">
         <v>4.47</v>
@@ -954,7 +1061,7 @@
         <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>4.88</v>
+        <v>6.11</v>
       </c>
       <c r="O9" t="n">
         <v>-0.88</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>12.26</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42513</v>
+        <v>42514</v>
       </c>
       <c r="H10" t="n">
-        <v>132.05</v>
+        <v>128.1</v>
       </c>
       <c r="I10" t="n">
         <v>130.5885485263562</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K10" t="n">
-        <v>7.1</v>
+        <v>3.89</v>
       </c>
       <c r="L10" t="n">
         <v>4.95</v>
@@ -1011,7 +1130,7 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>2.58</v>
+        <v>2.99</v>
       </c>
       <c r="O10" t="n">
         <v>6.11</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42516</v>
+        <v>42517</v>
       </c>
       <c r="H11" t="n">
-        <v>132.9</v>
+        <v>146</v>
       </c>
       <c r="I11" t="n">
         <v>140.5276270998557</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.75</v>
+        <v>-13.97</v>
       </c>
       <c r="L11" t="n">
-        <v>5.39</v>
+        <v>15.46</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>2.78</v>
       </c>
       <c r="N11" t="n">
-        <v>2.62</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="O11" t="n">
         <v>-2.99</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>13.35</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42704</v>
+        <v>42705</v>
       </c>
       <c r="H12" t="n">
-        <v>188.35</v>
+        <v>183.7</v>
       </c>
       <c r="I12" t="n">
         <v>184.2259009096191</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K12" t="n">
-        <v>29.01</v>
+        <v>25.82</v>
       </c>
       <c r="L12" t="n">
         <v>6.82</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="H13" t="n">
-        <v>187.35</v>
+        <v>190.4</v>
       </c>
       <c r="I13" t="n">
         <v>190.1249000432751</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.99</v>
+        <v>-3.65</v>
       </c>
       <c r="L13" t="n">
-        <v>2.72</v>
+        <v>4.9</v>
       </c>
       <c r="M13" t="n">
         <v>1.52</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>7.95</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42781</v>
+        <v>42782</v>
       </c>
       <c r="H14" t="n">
-        <v>197.85</v>
+        <v>196.2</v>
       </c>
       <c r="I14" t="n">
         <v>197.1394505958764</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K14" t="n">
-        <v>3.91</v>
+        <v>3.05</v>
       </c>
       <c r="L14" t="n">
         <v>2.26</v>
       </c>
       <c r="M14" t="n">
-        <v>0.41</v>
+        <v>0.66</v>
       </c>
       <c r="N14" t="n">
         <v>3.43</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42832</v>
+        <v>42835</v>
       </c>
       <c r="H15" t="n">
-        <v>198.05</v>
+        <v>205.7</v>
       </c>
       <c r="I15" t="n">
         <v>199.0608994601941</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-4.84</v>
       </c>
       <c r="L15" t="n">
         <v>8.720000000000001</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42899</v>
+        <v>42900</v>
       </c>
       <c r="H16" t="n">
-        <v>205.3</v>
+        <v>203.2</v>
       </c>
       <c r="I16" t="n">
         <v>203.6388681006884</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.19</v>
+        <v>-1.22</v>
       </c>
       <c r="L16" t="n">
         <v>2.99</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7.88</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42926</v>
+        <v>42927</v>
       </c>
       <c r="H17" t="n">
-        <v>194.8</v>
+        <v>198.95</v>
       </c>
       <c r="I17" t="n">
         <v>195.832173037008</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K17" t="n">
-        <v>4.13</v>
+        <v>2.09</v>
       </c>
       <c r="L17" t="n">
         <v>1.23</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.18</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H18" t="n">
-        <v>219.2</v>
+        <v>212.45</v>
       </c>
       <c r="I18" t="n">
         <v>213.7036733947338</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K18" t="n">
-        <v>10.18</v>
+        <v>6.79</v>
       </c>
       <c r="L18" t="n">
         <v>2.16</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>10.45</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42977</v>
+        <v>42978</v>
       </c>
       <c r="H19" t="n">
-        <v>230.7</v>
+        <v>234.4</v>
       </c>
       <c r="I19" t="n">
         <v>231.6335288971437</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
-        <v>-8.59</v>
+        <v>-10.33</v>
       </c>
       <c r="L19" t="n">
-        <v>9.32</v>
+        <v>11.51</v>
       </c>
       <c r="M19" t="n">
         <v>1.41</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>10.35</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H20" t="n">
-        <v>217.35</v>
+        <v>215.1</v>
       </c>
       <c r="I20" t="n">
         <v>215.170844058923</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K20" t="n">
-        <v>-7.27</v>
+        <v>-8.23</v>
       </c>
       <c r="L20" t="n">
-        <v>9.02</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>0.48</v>
+        <v>0.92</v>
       </c>
       <c r="N20" t="n">
         <v>6.59</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>10.66</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43024</v>
+        <v>43025</v>
       </c>
       <c r="H21" t="n">
-        <v>220.3</v>
+        <v>226.9</v>
       </c>
       <c r="I21" t="n">
         <v>225.734190192223</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.42</v>
+        <v>-5.49</v>
       </c>
       <c r="L21" t="n">
-        <v>2.95</v>
+        <v>5.88</v>
       </c>
       <c r="M21" t="n">
         <v>3.12</v>
       </c>
       <c r="N21" t="n">
-        <v>2.09</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>-1.04</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.58</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43074</v>
+        <v>43075</v>
       </c>
       <c r="H22" t="n">
-        <v>221.4</v>
+        <v>216.85</v>
       </c>
       <c r="I22" t="n">
         <v>217.7700863419476</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.42</v>
+        <v>-4.43</v>
       </c>
       <c r="L22" t="n">
         <v>5.16</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>9.07</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43087</v>
+        <v>43088</v>
       </c>
       <c r="H23" t="n">
-        <v>233.2</v>
+        <v>236.25</v>
       </c>
       <c r="I23" t="n">
         <v>235.727972882884</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K23" t="n">
-        <v>-7.54</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>8.279999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="M23" t="n">
         <v>2.11</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>8.56</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43101</v>
+        <v>43102</v>
       </c>
       <c r="H24" t="n">
-        <v>225</v>
+        <v>220.9</v>
       </c>
       <c r="I24" t="n">
         <v>220.9742143373895</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.76</v>
+        <v>-6.5</v>
       </c>
       <c r="L24" t="n">
-        <v>5.04</v>
+        <v>7.01</v>
       </c>
       <c r="M24" t="n">
         <v>0.77</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>9.42</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43257</v>
+        <v>43258</v>
       </c>
       <c r="H25" t="n">
-        <v>179.45</v>
+        <v>182.25</v>
       </c>
       <c r="I25" t="n">
         <v>179.4595454031249</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K25" t="n">
-        <v>18.76</v>
+        <v>17.5</v>
       </c>
       <c r="L25" t="n">
         <v>2.76</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>10.26</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43277</v>
+        <v>43278</v>
       </c>
       <c r="H26" t="n">
-        <v>181.9</v>
+        <v>166.95</v>
       </c>
       <c r="I26" t="n">
         <v>169.8190457416526</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.19</v>
+        <v>-8.4</v>
       </c>
       <c r="L26" t="n">
-        <v>2.8</v>
+        <v>9.52</v>
       </c>
       <c r="M26" t="n">
-        <v>1.14</v>
+        <v>1.81</v>
       </c>
       <c r="N26" t="n">
-        <v>3.53</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="O26" t="n">
         <v>1.56</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>15.21</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43357</v>
+        <v>43360</v>
       </c>
       <c r="H27" t="n">
-        <v>153.85</v>
+        <v>158.25</v>
       </c>
       <c r="I27" t="n">
         <v>156.6071483644737</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K27" t="n">
-        <v>7.85</v>
+        <v>5.21</v>
       </c>
       <c r="L27" t="n">
         <v>7.16</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>12.35</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43376</v>
+        <v>43377</v>
       </c>
       <c r="H28" t="n">
-        <v>164.65</v>
+        <v>143.15</v>
       </c>
       <c r="I28" t="n">
         <v>144.3810468160357</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" t="n">
-        <v>4.04</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>4.64</v>
+        <v>17.57</v>
       </c>
       <c r="M28" t="n">
         <v>2.75</v>
       </c>
       <c r="N28" t="n">
-        <v>2.59</v>
+        <v>13.06</v>
       </c>
       <c r="O28" t="n">
         <v>2.86</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>23.66</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43418</v>
+        <v>43419</v>
       </c>
       <c r="H29" t="n">
-        <v>136.1</v>
+        <v>138.85</v>
       </c>
       <c r="I29" t="n">
         <v>138.0545482801847</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K29" t="n">
-        <v>4.92</v>
+        <v>3</v>
       </c>
       <c r="L29" t="n">
         <v>16.91</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>17.93</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43474</v>
+        <v>43475</v>
       </c>
       <c r="H30" t="n">
-        <v>147.2</v>
+        <v>145.15</v>
       </c>
       <c r="I30" t="n">
         <v>146.1200639432291</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K30" t="n">
-        <v>6.01</v>
+        <v>4.54</v>
       </c>
       <c r="L30" t="n">
         <v>4.47</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>10.26</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H31" t="n">
-        <v>149.95</v>
+        <v>157.6</v>
       </c>
       <c r="I31" t="n">
         <v>151.7759239186172</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.31</v>
+        <v>-8.58</v>
       </c>
       <c r="L31" t="n">
-        <v>7.89</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>1.15</v>
       </c>
       <c r="N31" t="n">
-        <v>4.12</v>
+        <v>5.1</v>
       </c>
       <c r="O31" t="n">
         <v>-1.39</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>12.29</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43557</v>
+        <v>43558</v>
       </c>
       <c r="H32" t="n">
-        <v>165.85</v>
+        <v>157.9</v>
       </c>
       <c r="I32" t="n">
         <v>162.9172801287972</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K32" t="n">
-        <v>5.23</v>
+        <v>0.19</v>
       </c>
       <c r="L32" t="n">
         <v>5.04</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>13.66</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43581</v>
+        <v>43585</v>
       </c>
       <c r="H33" t="n">
-        <v>161.5</v>
+        <v>165.55</v>
       </c>
       <c r="I33" t="n">
         <v>161.6697835081755</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.28</v>
+        <v>-4.84</v>
       </c>
       <c r="L33" t="n">
-        <v>5.51</v>
+        <v>5.98</v>
       </c>
       <c r="M33" t="n">
         <v>1.17</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.89</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43650</v>
+        <v>43651</v>
       </c>
       <c r="H34" t="n">
-        <v>165.65</v>
+        <v>161.05</v>
       </c>
       <c r="I34" t="n">
         <v>161.984118685287</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K34" t="n">
-        <v>0.06</v>
+        <v>-2.72</v>
       </c>
       <c r="L34" t="n">
         <v>8.85</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>9.75</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43711</v>
+        <v>43712</v>
       </c>
       <c r="H35" t="n">
-        <v>154.65</v>
+        <v>158.1</v>
       </c>
       <c r="I35" t="n">
         <v>155.5362371910558</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K35" t="n">
-        <v>3.97</v>
+        <v>1.83</v>
       </c>
       <c r="L35" t="n">
         <v>2.95</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>14.42</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43809</v>
+        <v>43810</v>
       </c>
       <c r="H36" t="n">
-        <v>214.7</v>
+        <v>213</v>
       </c>
       <c r="I36" t="n">
         <v>213.9298329272571</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K36" t="n">
-        <v>35.8</v>
+        <v>34.72</v>
       </c>
       <c r="L36" t="n">
         <v>4.3</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>10.23</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43865</v>
+        <v>43866</v>
       </c>
       <c r="H37" t="n">
-        <v>211.1</v>
+        <v>221.8</v>
       </c>
       <c r="I37" t="n">
         <v>217.8791396732092</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K37" t="n">
-        <v>0.89</v>
+        <v>-4.13</v>
       </c>
       <c r="L37" t="n">
-        <v>4.53</v>
+        <v>5.49</v>
       </c>
       <c r="M37" t="n">
         <v>2.81</v>
       </c>
       <c r="N37" t="n">
-        <v>4.14</v>
+        <v>5.07</v>
       </c>
       <c r="O37" t="n">
         <v>-0.79</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>12.46</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43886</v>
+        <v>43887</v>
       </c>
       <c r="H38" t="n">
-        <v>201.1</v>
+        <v>197.4</v>
       </c>
       <c r="I38" t="n">
         <v>197.8340858908579</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>-9.33</v>
+        <v>-11</v>
       </c>
       <c r="L38" t="n">
-        <v>9.76</v>
+        <v>12.17</v>
       </c>
       <c r="M38" t="n">
         <v>0.19</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.85</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43985</v>
+        <v>43986</v>
       </c>
       <c r="H39" t="n">
-        <v>151.3</v>
+        <v>155.15</v>
       </c>
       <c r="I39" t="n">
         <v>152.7976872613896</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K39" t="n">
-        <v>23.35</v>
+        <v>21.4</v>
       </c>
       <c r="L39" t="n">
         <v>2.51</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>17.33</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44078</v>
+        <v>44081</v>
       </c>
       <c r="H40" t="n">
-        <v>176.4</v>
+        <v>174.95</v>
       </c>
       <c r="I40" t="n">
         <v>175.312387268494</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K40" t="n">
-        <v>13.7</v>
+        <v>12.76</v>
       </c>
       <c r="L40" t="n">
         <v>5.45</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.27</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44141</v>
+        <v>44144</v>
       </c>
       <c r="H41" t="n">
-        <v>157.55</v>
+        <v>163.6</v>
       </c>
       <c r="I41" t="n">
         <v>161.1924365100152</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K41" t="n">
-        <v>9.949999999999999</v>
+        <v>6.49</v>
       </c>
       <c r="L41" t="n">
         <v>9.43</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.04</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H42" t="n">
-        <v>169</v>
+        <v>165.9</v>
       </c>
       <c r="I42" t="n">
         <v>167.1327392762564</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K42" t="n">
-        <v>3.3</v>
+        <v>1.41</v>
       </c>
       <c r="L42" t="n">
         <v>5.23</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>12.51</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44244</v>
+        <v>44245</v>
       </c>
       <c r="H43" t="n">
-        <v>180.3</v>
+        <v>189.7</v>
       </c>
       <c r="I43" t="n">
         <v>185.7322792471582</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>-8.68</v>
+        <v>-14.35</v>
       </c>
       <c r="L43" t="n">
         <v>16</v>
@@ -2892,7 +3407,7 @@
         <v>2.77</v>
       </c>
       <c r="N43" t="n">
-        <v>4.02</v>
+        <v>5.21</v>
       </c>
       <c r="O43" t="n">
         <v>-1.83</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>12.38</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44295</v>
+        <v>44298</v>
       </c>
       <c r="H44" t="n">
-        <v>186.65</v>
+        <v>176.7</v>
       </c>
       <c r="I44" t="n">
         <v>183.4001078234928</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.61</v>
+        <v>-6.85</v>
       </c>
       <c r="L44" t="n">
-        <v>5.22</v>
+        <v>7.33</v>
       </c>
       <c r="M44" t="n">
         <v>4.6</v>
       </c>
       <c r="N44" t="n">
-        <v>5.08</v>
+        <v>5.33</v>
       </c>
       <c r="O44" t="n">
         <v>5.21</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,25 +3524,25 @@
         <v>11.65</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44323</v>
+        <v>44326</v>
       </c>
       <c r="H45" t="n">
-        <v>194.8</v>
+        <v>199.7</v>
       </c>
       <c r="I45" t="n">
         <v>195.4356296235364</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K45" t="n">
-        <v>-10.24</v>
+        <v>-13.02</v>
       </c>
       <c r="L45" t="n">
-        <v>11.23</v>
+        <v>13.3</v>
       </c>
       <c r="M45" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="N45" t="n">
         <v>2.66</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.74</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44386</v>
+        <v>44389</v>
       </c>
       <c r="H46" t="n">
-        <v>201.15</v>
+        <v>198.4</v>
       </c>
       <c r="I46" t="n">
         <v>200.4591023351222</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K46" t="n">
-        <v>0.73</v>
+        <v>-0.65</v>
       </c>
       <c r="L46" t="n">
         <v>3.61</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>5.93</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44434</v>
+        <v>44435</v>
       </c>
       <c r="H47" t="n">
-        <v>205.7</v>
+        <v>207.75</v>
       </c>
       <c r="I47" t="n">
         <v>206.3012480098608</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.68</v>
+        <v>-4.71</v>
       </c>
       <c r="L47" t="n">
-        <v>4.74</v>
+        <v>5.27</v>
       </c>
       <c r="M47" t="n">
         <v>0.89</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>6.65</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44454</v>
+        <v>44455</v>
       </c>
       <c r="H48" t="n">
-        <v>216.35</v>
+        <v>192.85</v>
       </c>
       <c r="I48" t="n">
         <v>206.9643991777836</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>4.14</v>
+        <v>-7.17</v>
       </c>
       <c r="L48" t="n">
-        <v>1.13</v>
+        <v>7.92</v>
       </c>
       <c r="M48" t="n">
-        <v>0.02</v>
+        <v>11.16</v>
       </c>
       <c r="N48" t="n">
-        <v>1.87</v>
+        <v>10.86</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>9.56</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44477</v>
+        <v>44480</v>
       </c>
       <c r="H49" t="n">
-        <v>197.65</v>
+        <v>199.95</v>
       </c>
       <c r="I49" t="n">
         <v>199.6727794971132</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.49</v>
+        <v>-3.68</v>
       </c>
       <c r="L49" t="n">
-        <v>3.11</v>
+        <v>3.86</v>
       </c>
       <c r="M49" t="n">
         <v>0.99</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>6.72</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H50" t="n">
-        <v>196.65</v>
+        <v>189.55</v>
       </c>
       <c r="I50" t="n">
         <v>193.4762353055393</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.65</v>
+        <v>-5.2</v>
       </c>
       <c r="L50" t="n">
-        <v>4.15</v>
+        <v>5.68</v>
       </c>
       <c r="M50" t="n">
         <v>0.25</v>
       </c>
       <c r="N50" t="n">
-        <v>2.76</v>
+        <v>3.61</v>
       </c>
       <c r="O50" t="n">
         <v>1.16</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H51" t="n">
-        <v>168.45</v>
+        <v>172.4</v>
       </c>
       <c r="I51" t="n">
         <v>171.7746203585732</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K51" t="n">
-        <v>11.13</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L51" t="n">
         <v>4.04</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>8.56</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H52" t="n">
-        <v>166.45</v>
+        <v>162.45</v>
       </c>
       <c r="I52" t="n">
         <v>164.1536525840824</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.45</v>
+        <v>-5.77</v>
       </c>
       <c r="L52" t="n">
-        <v>3.92</v>
+        <v>6.55</v>
       </c>
       <c r="M52" t="n">
         <v>0.55</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.25</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44651</v>
+        <v>44652</v>
       </c>
       <c r="H53" t="n">
-        <v>156.15</v>
+        <v>163.05</v>
       </c>
       <c r="I53" t="n">
         <v>160.9987948494202</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K53" t="n">
-        <v>3.88</v>
+        <v>-0.37</v>
       </c>
       <c r="L53" t="n">
         <v>7.57</v>
@@ -3462,7 +4097,7 @@
         <v>2.97</v>
       </c>
       <c r="N53" t="n">
-        <v>4.23</v>
+        <v>4.42</v>
       </c>
       <c r="O53" t="n">
         <v>-2.4</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44677</v>
+        <v>44678</v>
       </c>
       <c r="H54" t="n">
-        <v>162.35</v>
+        <v>159.45</v>
       </c>
       <c r="I54" t="n">
         <v>159.7939492595577</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.43</v>
+        <v>-2.21</v>
       </c>
       <c r="L54" t="n">
         <v>3.62</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44748</v>
+        <v>44749</v>
       </c>
       <c r="H55" t="n">
-        <v>138.6</v>
+        <v>142.3</v>
       </c>
       <c r="I55" t="n">
         <v>140.9927602695668</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K55" t="n">
-        <v>13.08</v>
+        <v>10.76</v>
       </c>
       <c r="L55" t="n">
         <v>1.79</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.56</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44799</v>
+        <v>44802</v>
       </c>
       <c r="H56" t="n">
-        <v>142.15</v>
+        <v>140.8</v>
       </c>
       <c r="I56" t="n">
         <v>141.0911084977096</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.11</v>
+        <v>-1.05</v>
       </c>
       <c r="L56" t="n">
         <v>8.19</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.78</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44888</v>
+        <v>44889</v>
       </c>
       <c r="H57" t="n">
-        <v>133.45</v>
+        <v>138.45</v>
       </c>
       <c r="I57" t="n">
         <v>135.7807652986165</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K57" t="n">
-        <v>5.22</v>
+        <v>1.67</v>
       </c>
       <c r="L57" t="n">
         <v>6.36</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>7.3</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H58" t="n">
-        <v>141.6</v>
+        <v>140.35</v>
       </c>
       <c r="I58" t="n">
         <v>141.4889498719623</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K58" t="n">
-        <v>2.28</v>
+        <v>1.37</v>
       </c>
       <c r="L58" t="n">
         <v>3.47</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1</v>
+        <v>0.92</v>
       </c>
       <c r="N58" t="n">
         <v>3.04</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>8.01</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44932</v>
+        <v>44935</v>
       </c>
       <c r="H59" t="n">
-        <v>149.4</v>
+        <v>150.35</v>
       </c>
       <c r="I59" t="n">
         <v>150.0002664829171</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.45</v>
+        <v>-7.13</v>
       </c>
       <c r="L59" t="n">
-        <v>7.05</v>
+        <v>7.94</v>
       </c>
       <c r="M59" t="n">
-        <v>0.51</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N59" t="n">
         <v>1.92</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.13</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44959</v>
+        <v>44960</v>
       </c>
       <c r="H60" t="n">
-        <v>143.6</v>
+        <v>141.05</v>
       </c>
       <c r="I60" t="n">
         <v>142.7116678552056</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.49</v>
+        <v>-6.19</v>
       </c>
       <c r="L60" t="n">
-        <v>5.32</v>
+        <v>7.55</v>
       </c>
       <c r="M60" t="n">
         <v>0.13</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>9.06</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45000</v>
+        <v>45001</v>
       </c>
       <c r="H61" t="n">
-        <v>142.7</v>
+        <v>152.25</v>
       </c>
       <c r="I61" t="n">
         <v>146.4638858238956</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.17</v>
+        <v>-7.94</v>
       </c>
       <c r="L61" t="n">
-        <v>3.58</v>
+        <v>8.51</v>
       </c>
       <c r="M61" t="n">
-        <v>0.92</v>
+        <v>1.54</v>
       </c>
       <c r="N61" t="n">
-        <v>2.3</v>
+        <v>6.69</v>
       </c>
       <c r="O61" t="n">
         <v>-1.78</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>9.4</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H62" t="n">
-        <v>149.2</v>
+        <v>142.55</v>
       </c>
       <c r="I62" t="n">
         <v>144.7552887182429</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K62" t="n">
-        <v>-2</v>
+        <v>-6.37</v>
       </c>
       <c r="L62" t="n">
-        <v>5.09</v>
+        <v>6.6</v>
       </c>
       <c r="M62" t="n">
-        <v>0.87</v>
+        <v>1.98</v>
       </c>
       <c r="N62" t="n">
-        <v>1.99</v>
+        <v>4.46</v>
       </c>
       <c r="O62" t="n">
         <v>6.69</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>8.91</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45042</v>
+        <v>45043</v>
       </c>
       <c r="H63" t="n">
-        <v>151.3</v>
+        <v>154.4</v>
       </c>
       <c r="I63" t="n">
         <v>153.2892223506172</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K63" t="n">
-        <v>-6.14</v>
+        <v>-8.31</v>
       </c>
       <c r="L63" t="n">
-        <v>6.31</v>
+        <v>8.59</v>
       </c>
       <c r="M63" t="n">
         <v>0.67</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.39</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45141</v>
+        <v>45142</v>
       </c>
       <c r="H64" t="n">
-        <v>160.05</v>
+        <v>156.6</v>
       </c>
       <c r="I64" t="n">
         <v>160.0163324710115</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K64" t="n">
-        <v>3.66</v>
+        <v>1.42</v>
       </c>
       <c r="L64" t="n">
         <v>2.07</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>9.56</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45177</v>
+        <v>45180</v>
       </c>
       <c r="H65" t="n">
-        <v>157.35</v>
+        <v>158.15</v>
       </c>
       <c r="I65" t="n">
         <v>158.055160339238</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.48</v>
+        <v>-0.99</v>
       </c>
       <c r="L65" t="n">
         <v>3.07</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>5.8</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45198</v>
+        <v>45202</v>
       </c>
       <c r="H66" t="n">
-        <v>150.25</v>
+        <v>147.85</v>
       </c>
       <c r="I66" t="n">
         <v>148.973926734155</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K66" t="n">
-        <v>-5</v>
+        <v>-6.51</v>
       </c>
       <c r="L66" t="n">
-        <v>6.35</v>
+        <v>6.67</v>
       </c>
       <c r="M66" t="n">
         <v>1.88</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>7.77</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45230</v>
+        <v>45231</v>
       </c>
       <c r="H67" t="n">
-        <v>151.4</v>
+        <v>155</v>
       </c>
       <c r="I67" t="n">
         <v>154.8812037336674</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.4</v>
+        <v>-4.84</v>
       </c>
       <c r="L67" t="n">
-        <v>5.07</v>
+        <v>5.41</v>
       </c>
       <c r="M67" t="n">
         <v>1.25</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.74</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45366</v>
+        <v>45369</v>
       </c>
       <c r="H68" t="n">
-        <v>270.55</v>
+        <v>268.65</v>
       </c>
       <c r="I68" t="n">
         <v>268.8549319325647</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K68" t="n">
-        <v>74.55</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="L68" t="n">
         <v>1.87</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>5</v>
+      </c>
+      <c r="U68" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>13.49</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45430</v>
+        <v>45433</v>
       </c>
       <c r="H69" t="n">
-        <v>290.25</v>
+        <v>297.15</v>
       </c>
       <c r="I69" t="n">
         <v>294.3129723070322</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K69" t="n">
-        <v>-8.039999999999999</v>
+        <v>-10.61</v>
       </c>
       <c r="L69" t="n">
-        <v>10.22</v>
+        <v>11.48</v>
       </c>
       <c r="M69" t="n">
         <v>3.86</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>10.65</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H70" t="n">
-        <v>307.35</v>
+        <v>267.7</v>
       </c>
       <c r="I70" t="n">
         <v>278.2036415715484</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K70" t="n">
-        <v>3.43</v>
+        <v>-9.91</v>
       </c>
       <c r="L70" t="n">
-        <v>4.11</v>
+        <v>12.01</v>
       </c>
       <c r="M70" t="n">
         <v>0.99</v>
       </c>
       <c r="N70" t="n">
-        <v>1.98</v>
+        <v>12.9</v>
       </c>
       <c r="O70" t="n">
         <v>2.38</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>22.22</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45497</v>
+        <v>45498</v>
       </c>
       <c r="H71" t="n">
-        <v>290.65</v>
+        <v>301</v>
       </c>
       <c r="I71" t="n">
         <v>296.3406853903959</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K71" t="n">
-        <v>-8.57</v>
+        <v>-12.44</v>
       </c>
       <c r="L71" t="n">
         <v>15.48</v>
@@ -4488,7 +5339,7 @@
         <v>3.75</v>
       </c>
       <c r="N71" t="n">
-        <v>2.94</v>
+        <v>3.56</v>
       </c>
       <c r="O71" t="n">
         <v>-12.9</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>12.17</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45553</v>
+        <v>45554</v>
       </c>
       <c r="H72" t="n">
-        <v>320.1</v>
+        <v>309</v>
       </c>
       <c r="I72" t="n">
         <v>317.9622034288229</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K72" t="n">
-        <v>6.35</v>
+        <v>2.66</v>
       </c>
       <c r="L72" t="n">
         <v>4.72</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45561</v>
+        <v>45562</v>
       </c>
       <c r="H73" t="n">
-        <v>328.65</v>
+        <v>349.8</v>
       </c>
       <c r="I73" t="n">
         <v>338.1432533555575</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K73" t="n">
-        <v>-6.36</v>
+        <v>-13.2</v>
       </c>
       <c r="L73" t="n">
-        <v>6.94</v>
+        <v>14.19</v>
       </c>
       <c r="M73" t="n">
         <v>0.61</v>
       </c>
       <c r="N73" t="n">
-        <v>2.09</v>
+        <v>6.44</v>
       </c>
       <c r="O73" t="n">
         <v>-3.47</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>10.87</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H74" t="n">
-        <v>324.05</v>
+        <v>319</v>
       </c>
       <c r="I74" t="n">
         <v>320.5574693691223</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K74" t="n">
-        <v>-7.36</v>
+        <v>-8.81</v>
       </c>
       <c r="L74" t="n">
-        <v>8.960000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="M74" t="n">
         <v>3.93</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>11.57</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H75" t="n">
-        <v>243.7</v>
+        <v>252.45</v>
       </c>
       <c r="I75" t="n">
         <v>249.3075782822187</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K75" t="n">
-        <v>23.61</v>
+        <v>20.86</v>
       </c>
       <c r="L75" t="n">
         <v>6.25</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>6</v>
+      </c>
+      <c r="U75" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>10.52</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45869</v>
+        <v>45870</v>
       </c>
       <c r="H76" t="n">
-        <v>313.65</v>
+        <v>302.7</v>
       </c>
       <c r="I76" t="n">
         <v>311.8601709035121</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K76" t="n">
-        <v>24.24</v>
+        <v>19.9</v>
       </c>
       <c r="L76" t="n">
         <v>4.06</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>6</v>
+      </c>
+      <c r="U76" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>9.84</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="H77" t="n">
-        <v>308.9</v>
+        <v>322</v>
       </c>
       <c r="I77" t="n">
         <v>315.0832936365106</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K77" t="n">
-        <v>-2.05</v>
+        <v>-6.38</v>
       </c>
       <c r="L77" t="n">
-        <v>5.45</v>
+        <v>6.66</v>
       </c>
       <c r="M77" t="n">
         <v>1.6</v>
       </c>
       <c r="N77" t="n">
-        <v>2.94</v>
+        <v>4.24</v>
       </c>
       <c r="O77" t="n">
         <v>-3.49</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="H78" t="n">
-        <v>357.95</v>
+        <v>344.7</v>
       </c>
       <c r="I78" t="n">
         <v>348.6521478653289</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K78" t="n">
-        <v>11.16</v>
+        <v>7.05</v>
       </c>
       <c r="L78" t="n">
         <v>3.73</v>
       </c>
       <c r="M78" t="n">
-        <v>0.38</v>
+        <v>0.54</v>
       </c>
       <c r="N78" t="n">
-        <v>2.29</v>
+        <v>3.7</v>
       </c>
       <c r="O78" t="n">
         <v>4.24</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>5</v>
+      </c>
+      <c r="U78" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H79" t="n">
-        <v>366.7</v>
+        <v>373.45</v>
       </c>
       <c r="I79" t="n">
         <v>369.9067097643338</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K79" t="n">
-        <v>-6.38</v>
+        <v>-8.34</v>
       </c>
       <c r="L79" t="n">
-        <v>6.64</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M79" t="n">
         <v>2.53</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>11.28</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H80" t="n">
-        <v>374.8</v>
+        <v>356.4</v>
       </c>
       <c r="I80" t="n">
         <v>359.3956578571285</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K80" t="n">
-        <v>0.36</v>
+        <v>-4.57</v>
       </c>
       <c r="L80" t="n">
-        <v>4.06</v>
+        <v>5.56</v>
       </c>
       <c r="M80" t="n">
         <v>4.51</v>
       </c>
       <c r="N80" t="n">
-        <v>3.48</v>
+        <v>4.91</v>
       </c>
       <c r="O80" t="n">
         <v>1.84</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>10.43</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="H81" t="n">
-        <v>307.95</v>
+        <v>312.1</v>
       </c>
       <c r="I81" t="n">
         <v>310.6622152028177</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K81" t="n">
-        <v>13.59</v>
+        <v>12.43</v>
       </c>
       <c r="L81" t="n">
         <v>3.21</v>
@@ -5067,7 +6038,19 @@
         <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,22 +6077,22 @@
         <v>12.13</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="H82" t="n">
-        <v>284.45</v>
+        <v>280.8</v>
       </c>
       <c r="I82" t="n">
         <v>283.9155409747761</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K82" t="n">
-        <v>-8.859999999999999</v>
+        <v>-10.03</v>
       </c>
       <c r="L82" t="n">
-        <v>9.16</v>
+        <v>11.37</v>
       </c>
       <c r="M82" t="n">
         <v>2.87</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5151,25 +6146,25 @@
         <v>9.92</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="H83" t="n">
-        <v>302.35</v>
+        <v>310.6</v>
       </c>
       <c r="I83" t="n">
         <v>306.9415088649404</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K83" t="n">
-        <v>-7.67</v>
+        <v>-10.61</v>
       </c>
       <c r="L83" t="n">
-        <v>11.11</v>
+        <v>12.8</v>
       </c>
       <c r="M83" t="n">
-        <v>3.18</v>
+        <v>4.18</v>
       </c>
       <c r="N83" t="n">
         <v>5.59</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>8.24</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="H84" t="n">
-        <v>312.9</v>
+        <v>303.85</v>
       </c>
       <c r="I84" t="n">
         <v>304.0079717013086</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K84" t="n">
-        <v>0.74</v>
+        <v>-2.17</v>
       </c>
       <c r="L84" t="n">
         <v>3.61</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>4</v>
+      </c>
+      <c r="U84" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -5289,6 +6308,14 @@
       <c r="Q85" t="n">
         <v>34</v>
       </c>
+      <c r="R85" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10247,7 +11274,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.5</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="6">
@@ -10257,7 +11284,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -10267,7 +11294,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8">
@@ -10277,7 +11304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -10287,7 +11314,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="10">
@@ -10297,7 +11324,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -10307,7 +11334,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -10317,7 +11344,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -10327,7 +11354,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>44.6</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="14">
@@ -10337,7 +11364,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.77</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="15">
@@ -10347,7 +11374,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.11</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="16">
@@ -10357,7 +11384,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.38</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="17">
@@ -10367,7 +11394,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>74.55</v>
+        <v>73.31999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -10377,7 +11404,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="19">
@@ -10387,7 +11414,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.81</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="20">
@@ -10397,7 +11424,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.07</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="21">
@@ -10407,7 +11434,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.91</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="22">
@@ -10417,7 +11444,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
@@ -10427,7 +11454,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -10437,7 +11464,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="25">
@@ -10447,7 +11474,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.26</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="26">
@@ -10457,7 +11484,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.05</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="27">
@@ -10477,7 +11504,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
